--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370141A3-E6EE-48C8-838F-E46F15AD8D23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A89D843-7416-4CD5-935B-6B01B68DEAD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -992,11 +992,11 @@
         <v>545651</v>
       </c>
       <c r="D10" s="33">
-        <v>440400.5</v>
+        <v>441732.5</v>
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="33">
-        <v>1355.5</v>
+        <v>23.5</v>
       </c>
       <c r="G10" s="33">
         <v>3240</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>1355.5</v>
+        <v>23.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A89D843-7416-4CD5-935B-6B01B68DEAD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A863F01A-A6FA-48D1-85CD-77834648D611}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="19">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -10147,14 +10147,20 @@
       <c r="B11" s="28">
         <v>46144</v>
       </c>
-      <c r="C11" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
+      <c r="C11" s="33">
+        <v>635011</v>
+      </c>
+      <c r="D11" s="33">
+        <v>546499</v>
+      </c>
+      <c r="E11" s="32">
+        <v>16</v>
+      </c>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33">
+        <v>3516</v>
+      </c>
+      <c r="H11" s="32"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -10963,12 +10969,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>456978</v>
+        <v>1091989</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -10976,7 +10982,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>2766</v>
+        <v>6282</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14439,11 +14445,10 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C11:H11"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A863F01A-A6FA-48D1-85CD-77834648D611}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729D317C-D11A-40CA-99D2-75E846880BE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1075,12 +1075,20 @@
       <c r="B13" s="28">
         <v>46146</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
+      <c r="C13" s="33">
+        <v>290296</v>
+      </c>
+      <c r="D13" s="33">
+        <v>248078.75</v>
+      </c>
       <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
+      <c r="F13" s="33">
+        <v>2066.25</v>
+      </c>
       <c r="G13" s="35"/>
-      <c r="H13" s="32"/>
+      <c r="H13" s="33">
+        <v>200</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1837,7 +1845,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>545651</v>
+        <v>835947</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1846,7 +1854,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>23.5</v>
+        <v>2089.75</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -1854,7 +1862,7 @@
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5638,11 +5646,19 @@
       <c r="B13" s="28">
         <v>46146</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="33">
+        <v>285008</v>
+      </c>
+      <c r="D13" s="33">
+        <v>241083.5</v>
+      </c>
+      <c r="E13" s="32">
+        <v>1226.5</v>
+      </c>
       <c r="F13" s="32"/>
-      <c r="G13" s="35"/>
+      <c r="G13" s="35">
+        <v>1296</v>
+      </c>
       <c r="H13" s="32"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -6400,12 +6416,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>236796</v>
+        <v>521804</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>182.5</v>
+        <v>1409</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6413,7 +6429,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>1518</v>
+        <v>2814</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10207,12 +10223,22 @@
       <c r="B13" s="28">
         <v>46146</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
+      <c r="C13" s="33">
+        <v>426537</v>
+      </c>
+      <c r="D13" s="33">
+        <v>360874</v>
+      </c>
       <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="32"/>
+      <c r="F13" s="33">
+        <v>1992</v>
+      </c>
+      <c r="G13" s="35">
+        <v>2328</v>
+      </c>
+      <c r="H13" s="33">
+        <v>50</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -10969,7 +10995,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1091989</v>
+        <v>1518526</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -10978,15 +11004,15 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>858</v>
+        <v>2850</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>6282</v>
+        <v>8610</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14446,6 +14472,9 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
@@ -14453,9 +14482,6 @@
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729D317C-D11A-40CA-99D2-75E846880BE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A1306D-BDD9-4AF3-A172-3E248AD9F9D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1108,12 +1108,22 @@
       <c r="B14" s="28">
         <v>46147</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32"/>
+      <c r="C14" s="33">
+        <v>470610</v>
+      </c>
+      <c r="D14" s="33">
+        <v>388937.25</v>
+      </c>
+      <c r="E14" s="32">
+        <v>3519</v>
+      </c>
       <c r="F14" s="32"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="32"/>
+      <c r="G14" s="35">
+        <v>2682</v>
+      </c>
+      <c r="H14" s="33">
+        <v>200</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1845,12 +1855,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>835947</v>
+        <v>1306557</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>0</v>
+        <v>3519</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -1858,11 +1868,11 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>3240</v>
+        <v>5922</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5679,11 +5689,19 @@
       <c r="B14" s="28">
         <v>46147</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+      <c r="C14" s="33">
+        <v>371226</v>
+      </c>
+      <c r="D14" s="33">
+        <v>310668</v>
+      </c>
       <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="35"/>
+      <c r="F14" s="33">
+        <v>789</v>
+      </c>
+      <c r="G14" s="35">
+        <v>2676</v>
+      </c>
       <c r="H14" s="32"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -6416,7 +6434,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>521804</v>
+        <v>893030</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6425,11 +6443,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>0</v>
+        <v>789</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>2814</v>
+        <v>5490</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10258,10 +10276,16 @@
       <c r="B14" s="28">
         <v>46147</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+      <c r="C14" s="33">
+        <v>518703</v>
+      </c>
+      <c r="D14" s="33">
+        <v>437893.5</v>
+      </c>
       <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
+      <c r="F14" s="33">
+        <v>81.5</v>
+      </c>
       <c r="G14" s="35"/>
       <c r="H14" s="32"/>
       <c r="I14" s="1"/>
@@ -10995,7 +11019,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1518526</v>
+        <v>2037229</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11004,7 +11028,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>2850</v>
+        <v>2931.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -14472,16 +14496,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C32:H32"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A1306D-BDD9-4AF3-A172-3E248AD9F9D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB73818-320A-43AE-8D58-E64BA00C6A6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1143,10 +1143,16 @@
       <c r="B15" s="28">
         <v>46148</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
+      <c r="C15" s="33">
+        <v>302093.92</v>
+      </c>
+      <c r="D15" s="33">
+        <v>190643.42</v>
+      </c>
       <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="F15" s="33">
+        <v>1643.58</v>
+      </c>
       <c r="G15" s="35"/>
       <c r="H15" s="32"/>
       <c r="I15" s="1"/>
@@ -1855,7 +1861,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1306557</v>
+        <v>1608650.92</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1864,7 +1870,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>2089.75</v>
+        <v>3733.33</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -5722,11 +5728,19 @@
       <c r="B15" s="28">
         <v>46148</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
+      <c r="C15" s="33">
+        <v>331431</v>
+      </c>
+      <c r="D15" s="33">
+        <v>280760.25</v>
+      </c>
       <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="35"/>
+      <c r="F15" s="33">
+        <v>17.75</v>
+      </c>
+      <c r="G15" s="35">
+        <v>2076</v>
+      </c>
       <c r="H15" s="32"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -6434,7 +6448,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>893030</v>
+        <v>1224461</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6443,11 +6457,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>789</v>
+        <v>806.75</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>5490</v>
+        <v>7566</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10307,12 +10321,23 @@
       <c r="B15" s="28">
         <v>46148</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
+      <c r="C15" s="33">
+        <v>324737</v>
+      </c>
+      <c r="D15" s="33">
+        <v>274038</v>
+      </c>
+      <c r="E15" s="33">
+        <v>50</v>
+      </c>
       <c r="F15" s="32"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="35">
+        <f>2190</f>
+        <v>2190</v>
+      </c>
+      <c r="H15" s="33">
+        <v>50</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -11019,12 +11044,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2037229</v>
+        <v>2361966</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11032,11 +11057,11 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>8610</v>
+        <v>10800</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14496,16 +14521,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB73818-320A-43AE-8D58-E64BA00C6A6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DF1177-6DA2-4286-BEA2-624A6EF1742B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1174,11 +1174,19 @@
       <c r="B16" s="28">
         <v>46149</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
+      <c r="C16" s="33">
+        <v>405449</v>
+      </c>
+      <c r="D16" s="33">
+        <v>331751.75</v>
+      </c>
+      <c r="E16" s="32">
+        <v>288.75</v>
+      </c>
       <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
+      <c r="G16" s="35">
+        <v>2880</v>
+      </c>
       <c r="H16" s="32"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1861,12 +1869,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1608650.92</v>
+        <v>2014099.92</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>3519</v>
+        <v>3807.75</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -1874,7 +1882,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>5922</v>
+        <v>8802</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -5761,9 +5769,15 @@
       <c r="B16" s="28">
         <v>46149</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
+      <c r="C16" s="33">
+        <v>242941</v>
+      </c>
+      <c r="D16" s="33">
+        <v>209789.5</v>
+      </c>
+      <c r="E16" s="32">
+        <v>3994.5</v>
+      </c>
       <c r="F16" s="32"/>
       <c r="G16" s="35"/>
       <c r="H16" s="32"/>
@@ -6448,12 +6462,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1224461</v>
+        <v>1467402</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>1409</v>
+        <v>5403.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -10327,7 +10341,7 @@
       <c r="D15" s="33">
         <v>274038</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="32">
         <v>50</v>
       </c>
       <c r="F15" s="32"/>
@@ -10357,11 +10371,19 @@
       <c r="B16" s="28">
         <v>46149</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
+      <c r="C16" s="33">
+        <v>355053</v>
+      </c>
+      <c r="D16" s="33">
+        <v>301508.25</v>
+      </c>
+      <c r="E16" s="32">
+        <v>9.25</v>
+      </c>
       <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
+      <c r="G16" s="35">
+        <v>2028</v>
+      </c>
       <c r="H16" s="32"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -11044,12 +11066,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2361966</v>
+        <v>2717019</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>66</v>
+        <v>75.25</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11057,7 +11079,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>10800</v>
+        <v>12828</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14521,16 +14543,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C32:H32"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DF1177-6DA2-4286-BEA2-624A6EF1742B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06EBF78-48F9-4956-A773-160BBB85045C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>MAY</t>
+  </si>
+  <si>
+    <t>NO TRIP</t>
   </si>
 </sst>
 </file>
@@ -1207,12 +1210,14 @@
       <c r="B17" s="28">
         <v>46150</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="32"/>
+      <c r="C17" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -5345,7 +5350,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C40:H40"/>
@@ -5357,6 +5362,7 @@
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C17:H17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -5800,11 +5806,19 @@
       <c r="B17" s="28">
         <v>46150</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
+      <c r="C17" s="33">
+        <v>257721</v>
+      </c>
+      <c r="D17" s="33">
+        <v>231897</v>
+      </c>
       <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="33">
+        <v>2345</v>
+      </c>
+      <c r="G17" s="35">
+        <v>1140</v>
+      </c>
       <c r="H17" s="32"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -6462,7 +6476,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1467402</v>
+        <v>1725123</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6471,11 +6485,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>806.75</v>
+        <v>3151.75</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>7566</v>
+        <v>8706</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10404,11 +10418,19 @@
       <c r="B17" s="28">
         <v>46150</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
+      <c r="C17" s="33">
+        <v>411243</v>
+      </c>
+      <c r="D17" s="33">
+        <v>346119.75</v>
+      </c>
       <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="33">
+        <v>610.25</v>
+      </c>
+      <c r="G17" s="35">
+        <v>2544</v>
+      </c>
       <c r="H17" s="32"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -11066,7 +11088,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2717019</v>
+        <v>3128262</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11075,11 +11097,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>2931.5</v>
+        <v>3541.75</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>12828</v>
+        <v>15372</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14543,16 +14565,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06EBF78-48F9-4956-A773-160BBB85045C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BCDD74-0ACE-4FE7-AE95-A90B96AD9049}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1291,9 +1291,15 @@
       <c r="B20" s="28">
         <v>46153</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
+      <c r="C20" s="33">
+        <v>312686.83</v>
+      </c>
+      <c r="D20" s="33">
+        <v>270424.33</v>
+      </c>
+      <c r="E20" s="32">
+        <v>47.33</v>
+      </c>
       <c r="F20" s="35"/>
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
@@ -1874,12 +1880,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2014099.92</v>
+        <v>2326786.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>3807.75</v>
+        <v>3855.08</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -5893,11 +5899,19 @@
       <c r="B20" s="28">
         <v>46153</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
+      <c r="C20" s="33">
+        <v>385347</v>
+      </c>
+      <c r="D20" s="33">
+        <v>324937.5</v>
+      </c>
       <c r="E20" s="32"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
+      <c r="F20" s="35">
+        <v>762.5</v>
+      </c>
+      <c r="G20" s="35">
+        <v>2880</v>
+      </c>
       <c r="H20" s="35"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -6476,7 +6490,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>1725123</v>
+        <v>2110470</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6485,11 +6499,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>3151.75</v>
+        <v>3914.25</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>8706</v>
+        <v>11586</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10505,12 +10519,22 @@
       <c r="B20" s="28">
         <v>46153</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
+      <c r="C20" s="33">
+        <v>306343</v>
+      </c>
+      <c r="D20" s="33">
+        <v>252932</v>
+      </c>
       <c r="E20" s="32"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="F20" s="35">
+        <v>2651.5</v>
+      </c>
+      <c r="G20" s="35">
+        <v>1632</v>
+      </c>
+      <c r="H20" s="35">
+        <v>50</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -11088,7 +11112,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3128262</v>
+        <v>3434605</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11097,15 +11121,15 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>3541.75</v>
+        <v>6193.25</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>15372</v>
+        <v>17004</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14565,16 +14589,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C32:H32"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BCDD74-0ACE-4FE7-AE95-A90B96AD9049}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449673A7-EC20-4B8B-AAA9-97C2BF714A44}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1322,12 +1322,22 @@
       <c r="B21" s="28">
         <v>46154</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
+      <c r="C21" s="33">
+        <v>302421</v>
+      </c>
+      <c r="D21" s="33">
+        <v>257779.79</v>
+      </c>
+      <c r="E21" s="32">
+        <v>189.54</v>
+      </c>
       <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
+      <c r="G21" s="35">
+        <v>2094</v>
+      </c>
+      <c r="H21" s="35">
+        <v>102.46</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1880,12 +1890,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2326786.75</v>
+        <v>2629207.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>3855.08</v>
+        <v>4044.62</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -1893,11 +1903,11 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>8802</v>
+        <v>10896</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>400</v>
+        <v>502.46</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5932,11 +5942,19 @@
       <c r="B21" s="28">
         <v>46154</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
+      <c r="C21" s="33">
+        <v>288065</v>
+      </c>
+      <c r="D21" s="33">
+        <v>245110</v>
+      </c>
+      <c r="E21" s="32">
+        <v>882</v>
+      </c>
       <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="G21" s="35">
+        <v>1446</v>
+      </c>
       <c r="H21" s="35"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -6490,12 +6508,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2110470</v>
+        <v>2398535</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>5403.5</v>
+        <v>6285.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6503,7 +6521,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>11586</v>
+        <v>13032</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10554,11 +10572,19 @@
       <c r="B21" s="28">
         <v>46154</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
+      <c r="C21" s="33">
+        <v>485304</v>
+      </c>
+      <c r="D21" s="33">
+        <v>404232</v>
+      </c>
+      <c r="E21" s="32">
+        <v>1516</v>
+      </c>
       <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="G21" s="35">
+        <v>3666</v>
+      </c>
       <c r="H21" s="35"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -11112,12 +11138,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3434605</v>
+        <v>3919909</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>75.25</v>
+        <v>1591.25</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11125,7 +11151,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>17004</v>
+        <v>20670</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14589,16 +14615,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449673A7-EC20-4B8B-AAA9-97C2BF714A44}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867193EE-D86D-47DE-89A9-16D9C8CB1690}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1357,10 +1357,16 @@
       <c r="B22" s="28">
         <v>46155</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
+      <c r="C22" s="33">
+        <v>346170.83</v>
+      </c>
+      <c r="D22" s="33">
+        <v>234441.33</v>
+      </c>
       <c r="E22" s="32"/>
-      <c r="F22" s="35"/>
+      <c r="F22" s="35">
+        <v>3.67</v>
+      </c>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
       <c r="I22" s="1"/>
@@ -1890,7 +1896,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2629207.75</v>
+        <v>2975378.58</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1899,7 +1905,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>3733.33</v>
+        <v>3737</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -5975,11 +5981,19 @@
       <c r="B22" s="28">
         <v>46155</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
+      <c r="C22" s="33">
+        <v>274505</v>
+      </c>
+      <c r="D22" s="33">
+        <v>231930.5</v>
+      </c>
+      <c r="E22" s="32">
+        <v>270.5</v>
+      </c>
       <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="G22" s="35">
+        <v>1944</v>
+      </c>
       <c r="H22" s="35"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -6508,12 +6522,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2398535</v>
+        <v>2673040</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>6285.5</v>
+        <v>6556</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6521,7 +6535,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>13032</v>
+        <v>14976</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10605,12 +10619,14 @@
       <c r="B22" s="28">
         <v>46155</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="C22" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -14614,17 +14630,18 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C22:H22"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867193EE-D86D-47DE-89A9-16D9C8CB1690}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1C78EF-7E9D-45BF-8996-4F3C257C3D5B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1388,11 +1388,19 @@
       <c r="B23" s="28">
         <v>46156</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="32"/>
+      <c r="C23" s="33">
+        <v>563496</v>
+      </c>
+      <c r="D23" s="33">
+        <v>497309.25</v>
+      </c>
+      <c r="E23" s="32">
+        <v>148.25</v>
+      </c>
       <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
+      <c r="G23" s="35">
+        <v>3420</v>
+      </c>
       <c r="H23" s="35"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1896,12 +1904,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2975378.58</v>
+        <v>3538874.58</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4044.62</v>
+        <v>4192.87</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -1909,7 +1917,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>10896</v>
+        <v>14316</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -6014,12 +6022,14 @@
       <c r="B23" s="28">
         <v>46156</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
+      <c r="C23" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -9998,7 +10008,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
@@ -10010,6 +10020,7 @@
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C23:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10646,12 +10657,22 @@
       <c r="B23" s="28">
         <v>46156</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
+      <c r="C23" s="33">
+        <v>344042</v>
+      </c>
+      <c r="D23" s="33">
+        <v>296318.25</v>
+      </c>
       <c r="E23" s="32"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
+      <c r="F23" s="35">
+        <v>310.75</v>
+      </c>
+      <c r="G23" s="35">
+        <v>1656</v>
+      </c>
+      <c r="H23" s="35">
+        <v>50</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -11154,7 +11175,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3919909</v>
+        <v>4263951</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11163,15 +11184,15 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6193.25</v>
+        <v>6504</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>20670</v>
+        <v>22326</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14631,17 +14652,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1C78EF-7E9D-45BF-8996-4F3C257C3D5B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A89C4D1-99E0-4B5F-B0D3-FF876620B608}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1421,11 +1421,19 @@
       <c r="B24" s="28">
         <v>46157</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
+      <c r="C24" s="33">
+        <v>339179</v>
+      </c>
+      <c r="D24" s="33">
+        <v>269272.5</v>
+      </c>
       <c r="E24" s="32"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
+      <c r="F24" s="35">
+        <v>2047.5</v>
+      </c>
+      <c r="G24" s="35">
+        <v>1994</v>
+      </c>
       <c r="H24" s="35"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1904,7 +1912,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3538874.58</v>
+        <v>3878053.58</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1913,11 +1921,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>3737</v>
+        <v>5784.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>14316</v>
+        <v>16310</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -6049,11 +6057,19 @@
       <c r="B24" s="28">
         <v>46157</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
+      <c r="C24" s="33">
+        <v>301997</v>
+      </c>
+      <c r="D24" s="33">
+        <v>255826.5</v>
+      </c>
       <c r="E24" s="32"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
+      <c r="F24" s="35">
+        <v>178.75</v>
+      </c>
+      <c r="G24" s="35">
+        <v>1200</v>
+      </c>
       <c r="H24" s="35"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -6532,7 +6548,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2673040</v>
+        <v>2975037</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6541,11 +6557,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>3914.25</v>
+        <v>4093</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>14976</v>
+        <v>16176</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10692,11 +10708,19 @@
       <c r="B24" s="28">
         <v>46157</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
+      <c r="C24" s="33">
+        <v>509099</v>
+      </c>
+      <c r="D24" s="33">
+        <v>434826.5</v>
+      </c>
       <c r="E24" s="32"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
+      <c r="F24" s="35">
+        <v>140.5</v>
+      </c>
+      <c r="G24" s="35">
+        <v>3192</v>
+      </c>
       <c r="H24" s="35"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -11175,7 +11199,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4263951</v>
+        <v>4773050</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11184,11 +11208,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6504</v>
+        <v>6644.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>22326</v>
+        <v>25518</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14652,17 +14676,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A89C4D1-99E0-4B5F-B0D3-FF876620B608}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53EC84F-02A3-4A3C-B3AC-55523479D528}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -14676,17 +14676,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53EC84F-02A3-4A3C-B3AC-55523479D528}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E6FF3D-4970-4B98-8378-09B627926CD2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -6090,14 +6090,20 @@
       <c r="B25" s="28">
         <v>46158</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
+      <c r="C25" s="33">
+        <v>272545</v>
+      </c>
+      <c r="D25" s="33">
+        <v>229232.5</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="35">
+        <v>21.5</v>
+      </c>
+      <c r="G25" s="35">
+        <v>2106</v>
+      </c>
+      <c r="H25" s="35"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -6548,7 +6554,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>2975037</v>
+        <v>3247582</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6557,11 +6563,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>4093</v>
+        <v>4114.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>16176</v>
+        <v>18282</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10024,14 +10030,13 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C33:H33"/>
@@ -14676,17 +14681,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E6FF3D-4970-4B98-8378-09B627926CD2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071DFB17-176F-4261-A3F5-6974E7FD3D8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1508,12 +1508,14 @@
       <c r="B27" s="28">
         <v>46160</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="31"/>
+      <c r="C27" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="42"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -5388,7 +5390,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C40:H40"/>
@@ -5401,6 +5403,7 @@
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C17:H17"/>
+    <mergeCell ref="C27:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6150,11 +6153,19 @@
       <c r="B27" s="28">
         <v>46160</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="14"/>
+      <c r="C27" s="12">
+        <v>491364</v>
+      </c>
+      <c r="D27" s="38">
+        <v>417927</v>
+      </c>
+      <c r="E27" s="14">
+        <v>205</v>
+      </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="34"/>
+      <c r="G27" s="34">
+        <v>3666</v>
+      </c>
       <c r="H27" s="31"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -6554,12 +6565,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3247582</v>
+        <v>3738946</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>6556</v>
+        <v>6761</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6567,7 +6578,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>18282</v>
+        <v>21948</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10800,12 +10811,22 @@
       <c r="B27" s="28">
         <v>46160</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="38"/>
+      <c r="C27" s="12">
+        <v>543461</v>
+      </c>
+      <c r="D27" s="38">
+        <v>461788.5</v>
+      </c>
       <c r="E27" s="14"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="31"/>
+      <c r="F27" s="12">
+        <v>14.5</v>
+      </c>
+      <c r="G27" s="34">
+        <v>2784</v>
+      </c>
+      <c r="H27" s="31">
+        <v>50</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -11204,7 +11225,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4773050</v>
+        <v>5316511</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11213,15 +11234,15 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6644.5</v>
+        <v>6659</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>25518</v>
+        <v>28302</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14681,17 +14702,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071DFB17-176F-4261-A3F5-6974E7FD3D8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5C7DA3-5B04-48ED-B60E-13251E6024B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1535,11 +1535,19 @@
       <c r="B28" s="28">
         <v>46161</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="38"/>
+      <c r="C28" s="12">
+        <v>442799</v>
+      </c>
+      <c r="D28" s="38">
+        <v>369506</v>
+      </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="34"/>
+      <c r="F28" s="12">
+        <v>8012</v>
+      </c>
+      <c r="G28" s="34">
+        <v>2742</v>
+      </c>
       <c r="H28" s="31"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1914,7 +1922,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3878053.58</v>
+        <v>4320852.58</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1923,11 +1931,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>5784.5</v>
+        <v>13796.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>16310</v>
+        <v>19052</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -6186,11 +6194,19 @@
       <c r="B28" s="28">
         <v>46161</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="14"/>
+      <c r="C28" s="12">
+        <v>320424</v>
+      </c>
+      <c r="D28" s="38">
+        <v>270121.5</v>
+      </c>
+      <c r="E28" s="14">
+        <v>768.5</v>
+      </c>
       <c r="F28" s="12"/>
-      <c r="G28" s="34"/>
+      <c r="G28" s="34">
+        <v>2076</v>
+      </c>
       <c r="H28" s="31"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -6565,12 +6581,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>3738946</v>
+        <v>4059370</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>6761</v>
+        <v>7529.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6578,7 +6594,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>21948</v>
+        <v>24024</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10846,11 +10862,19 @@
       <c r="B28" s="28">
         <v>46161</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="38"/>
+      <c r="C28" s="12">
+        <v>524541</v>
+      </c>
+      <c r="D28" s="38">
+        <v>448498.5</v>
+      </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="34"/>
+      <c r="F28" s="12">
+        <v>26.5</v>
+      </c>
+      <c r="G28" s="34">
+        <v>3300</v>
+      </c>
       <c r="H28" s="31"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -11225,7 +11249,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5316511</v>
+        <v>5841052</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11234,11 +11258,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6659</v>
+        <v>6685.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>28302</v>
+        <v>31602</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14702,17 +14726,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5C7DA3-5B04-48ED-B60E-13251E6024B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2A9100-3E52-4452-BB0C-BF516A24D5CD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -10866,14 +10866,15 @@
         <v>524541</v>
       </c>
       <c r="D28" s="38">
-        <v>448498.5</v>
+        <v>448138.5</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="12">
-        <v>26.5</v>
+        <v>386.5</v>
       </c>
       <c r="G28" s="34">
-        <v>3300</v>
+        <f>3660</f>
+        <v>3660</v>
       </c>
       <c r="H28" s="31"/>
       <c r="I28" s="1"/>
@@ -11258,11 +11259,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6685.5</v>
+        <v>7045.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>31602</v>
+        <v>31962</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14726,17 +14727,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2A9100-3E52-4452-BB0C-BF516A24D5CD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59779C8C-5FB8-4D96-9174-A0A1E44F3034}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1568,9 +1568,15 @@
       <c r="B29" s="28">
         <v>46162</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="14"/>
+      <c r="C29" s="12">
+        <v>392951</v>
+      </c>
+      <c r="D29" s="38">
+        <v>338312</v>
+      </c>
+      <c r="E29" s="14">
+        <v>512</v>
+      </c>
       <c r="F29" s="12"/>
       <c r="G29" s="34"/>
       <c r="H29" s="31"/>
@@ -1922,12 +1928,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4320852.58</v>
+        <v>4713803.58</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4192.87</v>
+        <v>4704.87</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6227,11 +6233,19 @@
       <c r="B29" s="28">
         <v>46162</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="38"/>
+      <c r="C29" s="12">
+        <v>294125</v>
+      </c>
+      <c r="D29" s="38">
+        <v>248850.5</v>
+      </c>
       <c r="E29" s="14"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="34"/>
+      <c r="F29" s="12">
+        <v>824.5</v>
+      </c>
+      <c r="G29" s="34">
+        <v>1296</v>
+      </c>
       <c r="H29" s="31"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -6581,7 +6595,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4059370</v>
+        <v>4353495</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6590,11 +6604,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>4114.5</v>
+        <v>4939</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>24024</v>
+        <v>25320</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10896,11 +10910,19 @@
       <c r="B29" s="28">
         <v>46162</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="14"/>
+      <c r="C29" s="12">
+        <v>276301</v>
+      </c>
+      <c r="D29" s="38">
+        <v>237123.25</v>
+      </c>
+      <c r="E29" s="14">
+        <v>334.25</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="34"/>
+      <c r="G29" s="34">
+        <v>1314</v>
+      </c>
       <c r="H29" s="31"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -11250,12 +11272,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5841052</v>
+        <v>6117353</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>1591.25</v>
+        <v>1925.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11263,7 +11285,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>31962</v>
+        <v>33276</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14727,17 +14749,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59779C8C-5FB8-4D96-9174-A0A1E44F3034}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B46A6D-181B-4D58-8981-399831ECEFCD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1599,9 +1599,15 @@
       <c r="B30" s="28">
         <v>46163</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="14"/>
+      <c r="C30" s="12">
+        <v>216025.17</v>
+      </c>
+      <c r="D30" s="38">
+        <v>130230.92</v>
+      </c>
+      <c r="E30" s="14">
+        <v>785.92</v>
+      </c>
       <c r="F30" s="12"/>
       <c r="G30" s="34"/>
       <c r="H30" s="31"/>
@@ -1928,12 +1934,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4713803.58</v>
+        <v>4929828.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4704.87</v>
+        <v>5490.79</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6266,11 +6272,19 @@
       <c r="B30" s="28">
         <v>46163</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="14"/>
+      <c r="C30" s="12">
+        <v>238493</v>
+      </c>
+      <c r="D30" s="38">
+        <v>194288</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="34"/>
+      <c r="G30" s="34">
+        <v>1158</v>
+      </c>
       <c r="H30" s="31"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -6595,12 +6609,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4353495</v>
+        <v>4591988</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>7529.5</v>
+        <v>7619.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6608,7 +6622,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>25320</v>
+        <v>26478</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10943,12 +10957,23 @@
       <c r="B30" s="28">
         <v>46163</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="14"/>
+      <c r="C30" s="12">
+        <v>412292</v>
+      </c>
+      <c r="D30" s="38">
+        <v>343192.5</v>
+      </c>
+      <c r="E30" s="14">
+        <v>1354.5</v>
+      </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="31"/>
+      <c r="G30" s="34">
+        <f>2166</f>
+        <v>2166</v>
+      </c>
+      <c r="H30" s="31">
+        <v>50</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="7"/>
@@ -11272,12 +11297,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>6117353</v>
+        <v>6529645</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>1925.5</v>
+        <v>3280</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11285,11 +11310,11 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>33276</v>
+        <v>35442</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14749,17 +14774,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B46A6D-181B-4D58-8981-399831ECEFCD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2ED214-DA70-4878-A3A0-6D5706309A04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1630,12 +1630,22 @@
       <c r="B31" s="28">
         <v>46164</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="38"/>
+      <c r="C31" s="12">
+        <v>343836</v>
+      </c>
+      <c r="D31" s="38">
+        <v>347471.73</v>
+      </c>
       <c r="E31" s="14"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="31"/>
+      <c r="F31" s="12">
+        <v>171.27</v>
+      </c>
+      <c r="G31" s="34">
+        <v>2268</v>
+      </c>
+      <c r="H31" s="31">
+        <v>109.27</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="18"/>
@@ -1655,14 +1665,20 @@
       <c r="B32" s="28">
         <v>46165</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="42"/>
+      <c r="C32" s="12">
+        <v>305232</v>
+      </c>
+      <c r="D32" s="38">
+        <v>213755.25</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="12">
+        <v>7.75</v>
+      </c>
+      <c r="G32" s="34">
+        <v>2070</v>
+      </c>
+      <c r="H32" s="31"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -1934,7 +1950,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4929828.75</v>
+        <v>5578896.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1943,15 +1959,15 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>13796.5</v>
+        <v>13975.52</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>19052</v>
+        <v>23390</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>502.46</v>
+        <v>611.73</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5410,7 +5426,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C40:H40"/>
@@ -5418,7 +5434,6 @@
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C32:H32"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C26:H26"/>
@@ -6305,11 +6320,19 @@
       <c r="B31" s="28">
         <v>46164</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="38"/>
+      <c r="C31" s="12">
+        <v>254943</v>
+      </c>
+      <c r="D31" s="38">
+        <v>214593.75</v>
+      </c>
       <c r="E31" s="14"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="34"/>
+      <c r="F31" s="12">
+        <v>147.25</v>
+      </c>
+      <c r="G31" s="34">
+        <v>1068</v>
+      </c>
       <c r="H31" s="31"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -6330,14 +6353,20 @@
       <c r="B32" s="28">
         <v>46165</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="42"/>
+      <c r="C32" s="12">
+        <v>231087</v>
+      </c>
+      <c r="D32" s="38">
+        <v>198523.5</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="12">
+        <v>123.5</v>
+      </c>
+      <c r="G32" s="34">
+        <v>1356</v>
+      </c>
+      <c r="H32" s="31"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -6609,7 +6638,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>4591988</v>
+        <v>5078018</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6618,11 +6647,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>4939</v>
+        <v>5209.75</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>26478</v>
+        <v>28902</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10085,7 +10114,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
@@ -10093,7 +10122,6 @@
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C32:H32"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C23:H23"/>
@@ -10993,12 +11021,14 @@
       <c r="B31" s="28">
         <v>46164</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="31"/>
+      <c r="C31" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="42"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="18"/>
@@ -11018,14 +11048,20 @@
       <c r="B32" s="28">
         <v>46165</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="42"/>
+      <c r="C32" s="12">
+        <v>542169</v>
+      </c>
+      <c r="D32" s="38">
+        <v>454961.25</v>
+      </c>
+      <c r="E32" s="14">
+        <v>1166.25</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="34">
+        <v>1602</v>
+      </c>
+      <c r="H32" s="31"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -11297,12 +11333,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>6529645</v>
+        <v>7071814</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>3280</v>
+        <v>4446.25</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11310,7 +11346,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>35442</v>
+        <v>37044</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14774,17 +14810,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C22:H22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2ED214-DA70-4878-A3A0-6D5706309A04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2742CB-55E6-4C08-8E6B-FC6DB04E4EB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1539,12 +1539,12 @@
         <v>442799</v>
       </c>
       <c r="D28" s="38">
-        <v>369506</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="12">
-        <v>8012</v>
-      </c>
+        <v>378776</v>
+      </c>
+      <c r="E28" s="14">
+        <v>1258</v>
+      </c>
+      <c r="F28" s="12"/>
       <c r="G28" s="34">
         <v>2742</v>
       </c>
@@ -1955,11 +1955,11 @@
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>5490.79</v>
+        <v>6748.79</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>13975.52</v>
+        <v>5963.52</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -14810,17 +14810,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2742CB-55E6-4C08-8E6B-FC6DB04E4EB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B26E61-07B6-4FAF-9BAF-6F1D7B863179}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -148,7 +148,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +247,13 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -357,7 +364,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -431,6 +438,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1725,10 +1744,16 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="39"/>
+      <c r="C34" s="44">
+        <v>88474</v>
+      </c>
+      <c r="D34" s="45">
+        <v>75999.25</v>
+      </c>
       <c r="E34" s="14"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="12">
+        <v>696.75</v>
+      </c>
       <c r="G34" s="34"/>
       <c r="H34" s="31"/>
       <c r="I34" s="1"/>
@@ -1950,7 +1975,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5578896.75</v>
+        <v>5667370.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1959,7 +1984,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>5963.52</v>
+        <v>6660.27</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -6413,11 +6438,19 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="14"/>
+      <c r="C34" s="43">
+        <v>278040</v>
+      </c>
+      <c r="D34" s="46">
+        <v>234187.5</v>
+      </c>
+      <c r="E34" s="14">
+        <v>84.5</v>
+      </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="34"/>
+      <c r="G34" s="34">
+        <v>2082</v>
+      </c>
       <c r="H34" s="31"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -6638,12 +6671,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5078018</v>
+        <v>5356058</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>7619.5</v>
+        <v>7704</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6651,7 +6684,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>28902</v>
+        <v>30984</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -11108,12 +11141,22 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="39"/>
+      <c r="C34" s="43">
+        <v>429899</v>
+      </c>
+      <c r="D34" s="46">
+        <v>386583</v>
+      </c>
       <c r="E34" s="14"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="31"/>
+      <c r="F34" s="12">
+        <v>7262</v>
+      </c>
+      <c r="G34" s="34">
+        <v>1740</v>
+      </c>
+      <c r="H34" s="31">
+        <v>50</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -11333,7 +11376,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>7071814</v>
+        <v>7501713</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11342,15 +11385,15 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>7045.5</v>
+        <v>14307.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>37044</v>
+        <v>38784</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14810,17 +14853,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B26E61-07B6-4FAF-9BAF-6F1D7B863179}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C481E83C-CB46-4572-9F56-F20E16CDFA29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -364,7 +364,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -431,6 +431,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -440,17 +443,18 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1043,14 +1047,14 @@
       <c r="B11" s="28">
         <v>46144</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="43"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1070,14 +1074,14 @@
       <c r="B12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1229,14 +1233,14 @@
       <c r="B17" s="28">
         <v>46150</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1256,14 +1260,14 @@
       <c r="B18" s="28">
         <v>46151</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1283,14 +1287,14 @@
       <c r="B19" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1473,14 +1477,14 @@
       <c r="B25" s="28">
         <v>46158</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -1500,14 +1504,14 @@
       <c r="B26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -1527,14 +1531,14 @@
       <c r="B27" s="28">
         <v>46160</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -1717,14 +1721,14 @@
       <c r="B33" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -1744,10 +1748,10 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="48">
         <v>88474</v>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="47">
         <v>75999.25</v>
       </c>
       <c r="E34" s="14"/>
@@ -1775,10 +1779,16 @@
       <c r="B35" s="28">
         <v>46168</v>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="39"/>
+      <c r="C35" s="48">
+        <v>216781</v>
+      </c>
+      <c r="D35" s="47">
+        <v>184597.75</v>
+      </c>
       <c r="E35" s="14"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="12">
+        <v>48.25</v>
+      </c>
       <c r="G35" s="34"/>
       <c r="H35" s="31"/>
       <c r="I35" s="1"/>
@@ -1800,7 +1810,7 @@
       <c r="B36" s="28">
         <v>46169</v>
       </c>
-      <c r="C36" s="25"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="39"/>
       <c r="E36" s="14"/>
       <c r="F36" s="12"/>
@@ -1825,7 +1835,7 @@
       <c r="B37" s="28">
         <v>46170</v>
       </c>
-      <c r="C37" s="25"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="39"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12"/>
@@ -1850,7 +1860,7 @@
       <c r="B38" s="28">
         <v>46171</v>
       </c>
-      <c r="C38" s="25"/>
+      <c r="C38" s="40"/>
       <c r="D38" s="39"/>
       <c r="E38" s="14"/>
       <c r="F38" s="12"/>
@@ -1875,14 +1885,14 @@
       <c r="B39" s="28">
         <v>46172</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="43"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -1902,14 +1912,14 @@
       <c r="B40" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -1950,12 +1960,12 @@
         <v>31</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="42"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -1975,7 +1985,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5667370.75</v>
+        <v>5884151.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -1984,7 +1994,7 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6660.27</v>
+        <v>6708.52</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -5723,14 +5733,14 @@
       <c r="B11" s="28">
         <v>46144</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="43"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -5750,14 +5760,14 @@
       <c r="B12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -5940,14 +5950,14 @@
       <c r="B18" s="28">
         <v>46151</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -5967,14 +5977,14 @@
       <c r="B19" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -6093,14 +6103,14 @@
       <c r="B23" s="28">
         <v>46156</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -6186,14 +6196,14 @@
       <c r="B26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -6411,14 +6421,14 @@
       <c r="B33" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -6438,10 +6448,10 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="44">
         <v>278040</v>
       </c>
-      <c r="D34" s="46">
+      <c r="D34" s="45">
         <v>234187.5</v>
       </c>
       <c r="E34" s="14">
@@ -6471,11 +6481,19 @@
       <c r="B35" s="28">
         <v>46168</v>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="14"/>
+      <c r="C35" s="12">
+        <v>236836</v>
+      </c>
+      <c r="D35" s="38">
+        <v>204773.5</v>
+      </c>
+      <c r="E35" s="14">
+        <v>150.5</v>
+      </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="34"/>
+      <c r="G35" s="34">
+        <v>1110</v>
+      </c>
       <c r="H35" s="31"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -6571,14 +6589,14 @@
       <c r="B39" s="28">
         <v>46172</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="43"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -6598,14 +6616,14 @@
       <c r="B40" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -6646,12 +6664,12 @@
         <v>31</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="42"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -6671,12 +6689,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5356058</v>
+        <v>5592894</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>7704</v>
+        <v>7854.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6684,7 +6702,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>30984</v>
+        <v>32094</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10450,14 +10468,14 @@
       <c r="B12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -10645,14 +10663,14 @@
       <c r="B18" s="28">
         <v>46151</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -10672,14 +10690,14 @@
       <c r="B19" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -10767,14 +10785,14 @@
       <c r="B22" s="28">
         <v>46155</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="43"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -10862,14 +10880,14 @@
       <c r="B25" s="28">
         <v>46158</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -10889,14 +10907,14 @@
       <c r="B26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -11054,14 +11072,14 @@
       <c r="B31" s="28">
         <v>46164</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="18"/>
@@ -11114,14 +11132,14 @@
       <c r="B33" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -11141,7 +11159,7 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="44">
         <v>429899</v>
       </c>
       <c r="D34" s="46">
@@ -11176,11 +11194,19 @@
       <c r="B35" s="28">
         <v>46168</v>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="14"/>
+      <c r="C35" s="12">
+        <v>416264</v>
+      </c>
+      <c r="D35" s="12">
+        <v>354823.25</v>
+      </c>
+      <c r="E35" s="14">
+        <v>1630.25</v>
+      </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="34"/>
+      <c r="G35" s="34">
+        <v>2352</v>
+      </c>
       <c r="H35" s="31"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -11276,14 +11302,14 @@
       <c r="B39" s="28">
         <v>46172</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="43"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -11303,14 +11329,14 @@
       <c r="B40" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -11351,12 +11377,12 @@
         <v>31</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="42"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -11376,12 +11402,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>7501713</v>
+        <v>7917977</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4446.25</v>
+        <v>6076.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11389,7 +11415,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>38784</v>
+        <v>41136</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14853,17 +14879,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C481E83C-CB46-4572-9F56-F20E16CDFA29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA313CA2-33FB-42E6-907F-360A7D6FC51C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="21">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>NO TRIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -434,15 +437,6 @@
     <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -455,6 +449,15 @@
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1047,14 +1050,14 @@
       <c r="B11" s="28">
         <v>46144</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="48"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1074,14 +1077,14 @@
       <c r="B12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1233,14 +1236,14 @@
       <c r="B17" s="28">
         <v>46150</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="43"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1260,14 +1263,14 @@
       <c r="B18" s="28">
         <v>46151</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1287,14 +1290,14 @@
       <c r="B19" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1477,14 +1480,14 @@
       <c r="B25" s="28">
         <v>46158</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -1504,14 +1507,14 @@
       <c r="B26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -1531,14 +1534,14 @@
       <c r="B27" s="28">
         <v>46160</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -1721,14 +1724,14 @@
       <c r="B33" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="43"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -1748,10 +1751,10 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="48">
+      <c r="C34" s="45">
         <v>88474</v>
       </c>
-      <c r="D34" s="47">
+      <c r="D34" s="44">
         <v>75999.25</v>
       </c>
       <c r="E34" s="14"/>
@@ -1779,10 +1782,10 @@
       <c r="B35" s="28">
         <v>46168</v>
       </c>
-      <c r="C35" s="48">
+      <c r="C35" s="45">
         <v>216781</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="44">
         <v>184597.75</v>
       </c>
       <c r="E35" s="14"/>
@@ -1810,11 +1813,19 @@
       <c r="B36" s="28">
         <v>46169</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="14"/>
+      <c r="C36" s="12">
+        <v>267784</v>
+      </c>
+      <c r="D36" s="38">
+        <v>233117.5</v>
+      </c>
+      <c r="E36" s="14">
+        <v>417.5</v>
+      </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="34"/>
+      <c r="G36" s="34">
+        <v>2064</v>
+      </c>
       <c r="H36" s="31"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -1837,7 +1848,9 @@
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="39"/>
-      <c r="E37" s="14"/>
+      <c r="E37" s="14" t="s">
+        <v>20</v>
+      </c>
       <c r="F37" s="12"/>
       <c r="G37" s="34"/>
       <c r="H37" s="31"/>
@@ -1885,14 +1898,14 @@
       <c r="B39" s="28">
         <v>46172</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C39" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="43"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -1912,14 +1925,14 @@
       <c r="B40" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="43"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="48"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -1960,12 +1973,12 @@
         <v>31</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="43"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="48"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -1985,12 +1998,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5884151.75</v>
+        <v>6151935.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>6748.79</v>
+        <v>7166.29</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -1998,7 +2011,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>23390</v>
+        <v>25454</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -5733,14 +5746,14 @@
       <c r="B11" s="28">
         <v>46144</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="48"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -5760,14 +5773,14 @@
       <c r="B12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -5950,14 +5963,14 @@
       <c r="B18" s="28">
         <v>46151</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -5977,14 +5990,14 @@
       <c r="B19" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -6103,14 +6116,14 @@
       <c r="B23" s="28">
         <v>46156</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -6196,14 +6209,14 @@
       <c r="B26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -6421,14 +6434,14 @@
       <c r="B33" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="43"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -6448,10 +6461,10 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="41">
         <v>278040</v>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="42">
         <v>234187.5</v>
       </c>
       <c r="E34" s="14">
@@ -6514,11 +6527,19 @@
       <c r="B36" s="28">
         <v>46169</v>
       </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="39"/>
+      <c r="C36" s="12">
+        <v>136970</v>
+      </c>
+      <c r="D36" s="38">
+        <v>116307.5</v>
+      </c>
       <c r="E36" s="14"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="34"/>
+      <c r="F36" s="12">
+        <v>130.5</v>
+      </c>
+      <c r="G36" s="34">
+        <v>768</v>
+      </c>
       <c r="H36" s="31"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -6589,14 +6610,14 @@
       <c r="B39" s="28">
         <v>46172</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C39" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="43"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -6616,14 +6637,14 @@
       <c r="B40" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="43"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="48"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -6664,12 +6685,12 @@
         <v>31</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="43"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="48"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -6689,7 +6710,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5592894</v>
+        <v>5729864</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6698,11 +6719,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>5209.75</v>
+        <v>5340.25</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>32094</v>
+        <v>32862</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -10468,14 +10489,14 @@
       <c r="B12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -10663,14 +10684,14 @@
       <c r="B18" s="28">
         <v>46151</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -10690,14 +10711,14 @@
       <c r="B19" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -10785,14 +10806,14 @@
       <c r="B22" s="28">
         <v>46155</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -10880,14 +10901,14 @@
       <c r="B25" s="28">
         <v>46158</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -10907,14 +10928,14 @@
       <c r="B26" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -11072,14 +11093,14 @@
       <c r="B31" s="28">
         <v>46164</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="43"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="48"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="18"/>
@@ -11132,14 +11153,14 @@
       <c r="B33" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="43"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -11159,10 +11180,10 @@
       <c r="B34" s="28">
         <v>46167</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="41">
         <v>429899</v>
       </c>
-      <c r="D34" s="46">
+      <c r="D34" s="43">
         <v>386583</v>
       </c>
       <c r="E34" s="14"/>
@@ -11227,11 +11248,19 @@
       <c r="B36" s="28">
         <v>46169</v>
       </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="39"/>
+      <c r="C36" s="12">
+        <v>253015</v>
+      </c>
+      <c r="D36" s="38">
+        <v>217959</v>
+      </c>
       <c r="E36" s="14"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="34"/>
+      <c r="F36" s="12">
+        <v>592</v>
+      </c>
+      <c r="G36" s="34">
+        <v>630</v>
+      </c>
       <c r="H36" s="31"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -11302,14 +11331,14 @@
       <c r="B39" s="28">
         <v>46172</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C39" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="43"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -11329,14 +11358,14 @@
       <c r="B40" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="43"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="48"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -11377,12 +11406,12 @@
         <v>31</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="43"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="48"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -11402,7 +11431,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>7917977</v>
+        <v>8170992</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -11411,11 +11440,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>14307.5</v>
+        <v>14899.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>41136</v>
+        <v>41766</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14879,17 +14908,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA313CA2-33FB-42E6-907F-360A7D6FC51C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB79804-E836-46F5-8366-7227EDDC6851}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>NO TRIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1846,13 +1843,19 @@
       <c r="B37" s="28">
         <v>46170</v>
       </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="14" t="s">
-        <v>20</v>
+      <c r="C37" s="40">
+        <v>314879</v>
+      </c>
+      <c r="D37" s="38">
+        <v>202069.5</v>
+      </c>
+      <c r="E37" s="14">
+        <v>1129.25</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="34"/>
+      <c r="G37" s="34">
+        <v>30</v>
+      </c>
       <c r="H37" s="31"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -1998,12 +2001,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>6151935.75</v>
+        <v>6466814.75</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>7166.29</v>
+        <v>8295.5400000000009</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -2011,7 +2014,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>25454</v>
+        <v>25484</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -6560,11 +6563,19 @@
       <c r="B37" s="28">
         <v>46170</v>
       </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="39"/>
+      <c r="C37" s="12">
+        <v>271800</v>
+      </c>
+      <c r="D37" s="12">
+        <v>230456.25</v>
+      </c>
       <c r="E37" s="14"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="34"/>
+      <c r="F37" s="12">
+        <v>79.75</v>
+      </c>
+      <c r="G37" s="34">
+        <v>1296</v>
+      </c>
       <c r="H37" s="31"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -6710,7 +6721,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>5729864</v>
+        <v>6001664</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
@@ -6719,11 +6730,11 @@
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>5340.25</v>
+        <v>5420</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>32862</v>
+        <v>34158</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -11281,11 +11292,19 @@
       <c r="B37" s="28">
         <v>46170</v>
       </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="14"/>
+      <c r="C37" s="12">
+        <v>236260</v>
+      </c>
+      <c r="D37" s="12">
+        <v>193075</v>
+      </c>
+      <c r="E37" s="14">
+        <v>2791</v>
+      </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="34"/>
+      <c r="G37" s="34">
+        <v>948</v>
+      </c>
       <c r="H37" s="31"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -11431,12 +11450,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>8170992</v>
+        <v>8407252</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>6076.5</v>
+        <v>8867.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -11444,7 +11463,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>41766</v>
+        <v>42714</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -14908,17 +14927,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB79804-E836-46F5-8366-7227EDDC6851}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D789DCF7-C891-4C29-AD0A-86BDBCB4AB25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -14927,17 +14927,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D789DCF7-C891-4C29-AD0A-86BDBCB4AB25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A3E467-18F3-45A4-9808-3D03B86DDB73}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -14927,17 +14927,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A3E467-18F3-45A4-9808-3D03B86DDB73}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B84630-1C33-4B26-8724-2CCD79D0E83E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -364,7 +364,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -404,9 +404,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -428,9 +425,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -980,7 +974,7 @@
       <c r="C9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="36" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="24" t="s">
@@ -1011,23 +1005,23 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <v>46143</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <v>545651</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>441732.5</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33">
+      <c r="E10" s="31"/>
+      <c r="F10" s="32">
         <v>23.5</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="32">
         <v>3240</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1044,17 +1038,17 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>46144</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1071,17 +1065,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1098,21 +1092,21 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>46146</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <v>290296</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <v>248078.75</v>
       </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33">
+      <c r="E13" s="31"/>
+      <c r="F13" s="32">
         <v>2066.25</v>
       </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="33">
+      <c r="G13" s="34"/>
+      <c r="H13" s="32">
         <v>200</v>
       </c>
       <c r="I13" s="1"/>
@@ -1131,23 +1125,23 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>46147</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="32">
         <v>470610</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="32">
         <v>388937.25</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="31">
         <v>3519</v>
       </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="35">
+      <c r="F14" s="31"/>
+      <c r="G14" s="34">
         <v>2682</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="32">
         <v>200</v>
       </c>
       <c r="I14" s="1"/>
@@ -1166,21 +1160,21 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <v>46148</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="32">
         <v>302093.92</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>190643.42</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="33">
+      <c r="E15" s="31"/>
+      <c r="F15" s="32">
         <v>1643.58</v>
       </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1197,23 +1191,23 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>46149</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="32">
         <v>405449</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>331751.75</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="31">
         <v>288.75</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35">
+      <c r="F16" s="31"/>
+      <c r="G16" s="34">
         <v>2880</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1230,17 +1224,17 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <v>46150</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="48"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1257,17 +1251,17 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="27">
         <v>46151</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1284,17 +1278,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1311,21 +1305,21 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <v>46153</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="32">
         <v>312686.83</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <v>270424.33</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="31">
         <v>47.33</v>
       </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1342,23 +1336,23 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>46154</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="32">
         <v>302421</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="32">
         <v>257779.79</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <v>189.54</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35">
+      <c r="F21" s="34"/>
+      <c r="G21" s="34">
         <v>2094</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="34">
         <v>102.46</v>
       </c>
       <c r="I21" s="1"/>
@@ -1377,21 +1371,21 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>46155</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="32">
         <v>346170.83</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="32">
         <v>234441.33</v>
       </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="35">
+      <c r="E22" s="31"/>
+      <c r="F22" s="34">
         <v>3.67</v>
       </c>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1408,23 +1402,23 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <v>46156</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="32">
         <v>563496</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="32">
         <v>497309.25</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="31">
         <v>148.25</v>
       </c>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35">
+      <c r="F23" s="34"/>
+      <c r="G23" s="34">
         <v>3420</v>
       </c>
-      <c r="H23" s="35"/>
+      <c r="H23" s="34"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -1441,23 +1435,23 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="27">
         <v>46157</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="32">
         <v>339179</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <v>269272.5</v>
       </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="35">
+      <c r="E24" s="31"/>
+      <c r="F24" s="34">
         <v>2047.5</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="34">
         <v>1994</v>
       </c>
-      <c r="H24" s="35"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="7"/>
@@ -1474,17 +1468,17 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="27">
         <v>46158</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="46"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -1501,17 +1495,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -1528,17 +1522,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="27">
         <v>46160</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="46"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -1555,23 +1549,23 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="27">
         <v>46161</v>
       </c>
       <c r="C28" s="12">
         <v>442799</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="37">
         <v>378776</v>
       </c>
       <c r="E28" s="14">
         <v>1258</v>
       </c>
       <c r="F28" s="12"/>
-      <c r="G28" s="34">
+      <c r="G28" s="33">
         <v>2742</v>
       </c>
-      <c r="H28" s="31"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -1588,21 +1582,21 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>46162</v>
       </c>
       <c r="C29" s="12">
         <v>392951</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="37">
         <v>338312</v>
       </c>
       <c r="E29" s="14">
         <v>512</v>
       </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="31"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="7"/>
@@ -1619,21 +1613,21 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <v>46163</v>
       </c>
       <c r="C30" s="12">
         <v>216025.17</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="37">
         <v>130230.92</v>
       </c>
       <c r="E30" s="14">
         <v>785.92</v>
       </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="31"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="7"/>
@@ -1650,23 +1644,23 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>46164</v>
       </c>
       <c r="C31" s="12">
         <v>343836</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="37">
         <v>347471.73</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="12">
         <v>171.27</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="33">
         <v>2268</v>
       </c>
-      <c r="H31" s="31">
+      <c r="H31" s="30">
         <v>109.27</v>
       </c>
       <c r="I31" s="1"/>
@@ -1685,23 +1679,23 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>46165</v>
       </c>
       <c r="C32" s="12">
         <v>305232</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="37">
         <v>213755.25</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="12">
         <v>7.75</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="33">
         <v>2070</v>
       </c>
-      <c r="H32" s="31"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -1718,17 +1712,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="46"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -1745,21 +1739,21 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>46167</v>
       </c>
-      <c r="C34" s="45">
+      <c r="C34" s="43">
         <v>88474</v>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="42">
         <v>75999.25</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12">
         <v>696.75</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="31"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="30"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -1776,21 +1770,21 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <v>46168</v>
       </c>
-      <c r="C35" s="45">
+      <c r="C35" s="43">
         <v>216781</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="42">
         <v>184597.75</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="12">
         <v>48.25</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="31"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -1807,23 +1801,23 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <v>46169</v>
       </c>
       <c r="C36" s="12">
         <v>267784</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="37">
         <v>233117.5</v>
       </c>
       <c r="E36" s="14">
         <v>417.5</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="34">
+      <c r="G36" s="33">
         <v>2064</v>
       </c>
-      <c r="H36" s="31"/>
+      <c r="H36" s="30"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -1840,23 +1834,23 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <v>46170</v>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="38">
         <v>314879</v>
       </c>
-      <c r="D37" s="38">
+      <c r="D37" s="37">
         <v>202069.5</v>
       </c>
       <c r="E37" s="14">
         <v>1129.25</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="34">
+      <c r="G37" s="33">
         <v>30</v>
       </c>
-      <c r="H37" s="31"/>
+      <c r="H37" s="30"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -1873,15 +1867,21 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <v>46171</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="39"/>
+      <c r="C38" s="38">
+        <v>374801</v>
+      </c>
+      <c r="D38" s="37">
+        <v>335870</v>
+      </c>
       <c r="E38" s="14"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="31"/>
+      <c r="F38" s="12">
+        <v>183</v>
+      </c>
+      <c r="G38" s="33"/>
+      <c r="H38" s="30"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7"/>
@@ -1898,17 +1898,17 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="27">
         <v>46172</v>
       </c>
-      <c r="C39" s="46" t="s">
+      <c r="C39" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -1925,17 +1925,17 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="46" t="s">
+      <c r="C40" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="48"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="46"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -1952,12 +1952,12 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="28"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
       <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -1975,13 +1975,13 @@
       <c r="A42" s="22">
         <v>31</v>
       </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="48"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="46"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -1995,22 +1995,22 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19" ht="15">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="28"/>
+      <c r="B43" s="27"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>6466814.75</v>
+        <v>6841615.75</v>
       </c>
       <c r="D43" s="17"/>
-      <c r="E43" s="29">
+      <c r="E43" s="28">
         <f>SUM(E10:E42)</f>
         <v>8295.5400000000009</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>6708.52</v>
+        <v>6891.52</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="44" spans="1:19" ht="15">
       <c r="A44" s="1"/>
-      <c r="B44" s="30"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="26"/>
+      <c r="E44" s="25"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="1"/>
@@ -5682,7 +5682,7 @@
       <c r="C9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="36" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="24" t="s">
@@ -5713,23 +5713,23 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <v>46143</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <v>236796</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>196732.5</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>182.5</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="33">
+      <c r="F10" s="31"/>
+      <c r="G10" s="32">
         <v>1518</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -5746,17 +5746,17 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>46144</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -5773,17 +5773,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -5800,23 +5800,23 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>46146</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <v>285008</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <v>241083.5</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="31">
         <v>1226.5</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="35">
+      <c r="F13" s="31"/>
+      <c r="G13" s="34">
         <v>1296</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="31"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -5833,23 +5833,23 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>46147</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="32">
         <v>371226</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="32">
         <v>310668</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33">
+      <c r="E14" s="31"/>
+      <c r="F14" s="32">
         <v>789</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="34">
         <v>2676</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="31"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -5866,23 +5866,23 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <v>46148</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="32">
         <v>331431</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>280760.25</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="33">
+      <c r="E15" s="31"/>
+      <c r="F15" s="32">
         <v>17.75</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="34">
         <v>2076</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -5899,21 +5899,21 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>46149</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="32">
         <v>242941</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>209789.5</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="31">
         <v>3994.5</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="32"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -5930,23 +5930,23 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <v>46150</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="32">
         <v>257721</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>231897</v>
       </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33">
+      <c r="E17" s="31"/>
+      <c r="F17" s="32">
         <v>2345</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="34">
         <v>1140</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -5963,17 +5963,17 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="27">
         <v>46151</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -5990,17 +5990,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -6017,23 +6017,23 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <v>46153</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="32">
         <v>385347</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <v>324937.5</v>
       </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="35">
+      <c r="E20" s="31"/>
+      <c r="F20" s="34">
         <v>762.5</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>2880</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -6050,23 +6050,23 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>46154</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="32">
         <v>288065</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="32">
         <v>245110</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <v>882</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35">
+      <c r="F21" s="34"/>
+      <c r="G21" s="34">
         <v>1446</v>
       </c>
-      <c r="H21" s="35"/>
+      <c r="H21" s="34"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -6083,23 +6083,23 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>46155</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="32">
         <v>274505</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="32">
         <v>231930.5</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="31">
         <v>270.5</v>
       </c>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35">
+      <c r="F22" s="34"/>
+      <c r="G22" s="34">
         <v>1944</v>
       </c>
-      <c r="H22" s="35"/>
+      <c r="H22" s="34"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -6116,17 +6116,17 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <v>46156</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="48"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -6143,23 +6143,23 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="27">
         <v>46157</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="32">
         <v>301997</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <v>255826.5</v>
       </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="35">
+      <c r="E24" s="31"/>
+      <c r="F24" s="34">
         <v>178.75</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="34">
         <v>1200</v>
       </c>
-      <c r="H24" s="35"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="7"/>
@@ -6176,23 +6176,23 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="27">
         <v>46158</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="32">
         <v>272545</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="32">
         <v>229232.5</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="35">
+      <c r="E25" s="31"/>
+      <c r="F25" s="34">
         <v>21.5</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="34">
         <v>2106</v>
       </c>
-      <c r="H25" s="35"/>
+      <c r="H25" s="34"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -6209,17 +6209,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -6236,23 +6236,23 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="27">
         <v>46160</v>
       </c>
       <c r="C27" s="12">
         <v>491364</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <v>417927</v>
       </c>
       <c r="E27" s="14">
         <v>205</v>
       </c>
       <c r="F27" s="12"/>
-      <c r="G27" s="34">
+      <c r="G27" s="33">
         <v>3666</v>
       </c>
-      <c r="H27" s="31"/>
+      <c r="H27" s="30"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -6269,23 +6269,23 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="27">
         <v>46161</v>
       </c>
       <c r="C28" s="12">
         <v>320424</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="37">
         <v>270121.5</v>
       </c>
       <c r="E28" s="14">
         <v>768.5</v>
       </c>
       <c r="F28" s="12"/>
-      <c r="G28" s="34">
+      <c r="G28" s="33">
         <v>2076</v>
       </c>
-      <c r="H28" s="31"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -6302,23 +6302,23 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>46162</v>
       </c>
       <c r="C29" s="12">
         <v>294125</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="37">
         <v>248850.5</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="12">
         <v>824.5</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="33">
         <v>1296</v>
       </c>
-      <c r="H29" s="31"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="7"/>
@@ -6335,23 +6335,23 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <v>46163</v>
       </c>
       <c r="C30" s="12">
         <v>238493</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="37">
         <v>194288</v>
       </c>
       <c r="E30" s="14">
         <v>90</v>
       </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="34">
+      <c r="G30" s="33">
         <v>1158</v>
       </c>
-      <c r="H30" s="31"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="7"/>
@@ -6368,23 +6368,23 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>46164</v>
       </c>
       <c r="C31" s="12">
         <v>254943</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="37">
         <v>214593.75</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="12">
         <v>147.25</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="33">
         <v>1068</v>
       </c>
-      <c r="H31" s="31"/>
+      <c r="H31" s="30"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="18"/>
@@ -6401,23 +6401,23 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>46165</v>
       </c>
       <c r="C32" s="12">
         <v>231087</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="37">
         <v>198523.5</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="12">
         <v>123.5</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="33">
         <v>1356</v>
       </c>
-      <c r="H32" s="31"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -6434,17 +6434,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="46"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -6461,23 +6461,23 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>46167</v>
       </c>
-      <c r="C34" s="41">
+      <c r="C34" s="39">
         <v>278040</v>
       </c>
-      <c r="D34" s="42">
+      <c r="D34" s="40">
         <v>234187.5</v>
       </c>
       <c r="E34" s="14">
         <v>84.5</v>
       </c>
       <c r="F34" s="12"/>
-      <c r="G34" s="34">
+      <c r="G34" s="33">
         <v>2082</v>
       </c>
-      <c r="H34" s="31"/>
+      <c r="H34" s="30"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -6494,23 +6494,23 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <v>46168</v>
       </c>
       <c r="C35" s="12">
         <v>236836</v>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="37">
         <v>204773.5</v>
       </c>
       <c r="E35" s="14">
         <v>150.5</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="34">
+      <c r="G35" s="33">
         <v>1110</v>
       </c>
-      <c r="H35" s="31"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -6527,23 +6527,23 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <v>46169</v>
       </c>
       <c r="C36" s="12">
         <v>136970</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="37">
         <v>116307.5</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12">
         <v>130.5</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="33">
         <v>768</v>
       </c>
-      <c r="H36" s="31"/>
+      <c r="H36" s="30"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -6560,7 +6560,7 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <v>46170</v>
       </c>
       <c r="C37" s="12">
@@ -6573,10 +6573,10 @@
       <c r="F37" s="12">
         <v>79.75</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="33">
         <v>1296</v>
       </c>
-      <c r="H37" s="31"/>
+      <c r="H37" s="30"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -6593,15 +6593,23 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <v>46171</v>
       </c>
-      <c r="C38" s="25"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="14"/>
+      <c r="C38" s="12">
+        <v>277420</v>
+      </c>
+      <c r="D38" s="12">
+        <v>241276</v>
+      </c>
+      <c r="E38" s="14">
+        <v>144</v>
+      </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="31"/>
+      <c r="G38" s="33">
+        <v>1314</v>
+      </c>
+      <c r="H38" s="30"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7"/>
@@ -6618,17 +6626,17 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="27">
         <v>46172</v>
       </c>
-      <c r="C39" s="46" t="s">
+      <c r="C39" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -6645,17 +6653,17 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="46" t="s">
+      <c r="C40" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="48"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="46"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -6672,12 +6680,12 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="28"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
       <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -6695,13 +6703,13 @@
       <c r="A42" s="22">
         <v>31</v>
       </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="48"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="46"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -6715,18 +6723,18 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19" ht="15">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="28"/>
+      <c r="B43" s="27"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>6001664</v>
+        <v>6279084</v>
       </c>
       <c r="D43" s="17"/>
-      <c r="E43" s="29">
+      <c r="E43" s="28">
         <f>SUM(E10:E42)</f>
-        <v>7854.5</v>
+        <v>7998.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
@@ -6734,7 +6742,7 @@
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>34158</v>
+        <v>35472</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
@@ -6757,7 +6765,7 @@
       <c r="B44" s="1"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="26"/>
+      <c r="E44" s="25"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="1"/>
@@ -10400,7 +10408,7 @@
       <c r="C9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="36" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="24" t="s">
@@ -10431,23 +10439,23 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <v>46143</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <v>456978</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>385311</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33">
+      <c r="E10" s="31"/>
+      <c r="F10" s="32">
         <v>858</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="32">
         <v>2766</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -10464,23 +10472,23 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>46144</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="32">
         <v>635011</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="32">
         <v>546499</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <v>16</v>
       </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33">
+      <c r="F11" s="32"/>
+      <c r="G11" s="32">
         <v>3516</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="31"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -10497,17 +10505,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -10524,23 +10532,23 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>46146</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <v>426537</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <v>360874</v>
       </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33">
+      <c r="E13" s="31"/>
+      <c r="F13" s="32">
         <v>1992</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="34">
         <v>2328</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <v>50</v>
       </c>
       <c r="I13" s="1"/>
@@ -10559,21 +10567,21 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>46147</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="32">
         <v>518703</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="32">
         <v>437893.5</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33">
+      <c r="E14" s="31"/>
+      <c r="F14" s="32">
         <v>81.5</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="32"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="31"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -10590,24 +10598,24 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <v>46148</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="32">
         <v>324737</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="32">
         <v>274038</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="31">
         <v>50</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="35">
+      <c r="F15" s="31"/>
+      <c r="G15" s="34">
         <f>2190</f>
         <v>2190</v>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="32">
         <v>50</v>
       </c>
       <c r="I15" s="1"/>
@@ -10626,23 +10634,23 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>46149</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="32">
         <v>355053</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <v>301508.25</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="31">
         <v>9.25</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35">
+      <c r="F16" s="31"/>
+      <c r="G16" s="34">
         <v>2028</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="31"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -10659,23 +10667,23 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <v>46150</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="32">
         <v>411243</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="32">
         <v>346119.75</v>
       </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33">
+      <c r="E17" s="31"/>
+      <c r="F17" s="32">
         <v>610.25</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="34">
         <v>2544</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -10692,17 +10700,17 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="27">
         <v>46151</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -10719,17 +10727,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -10746,23 +10754,23 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <v>46153</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="32">
         <v>306343</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <v>252932</v>
       </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="35">
+      <c r="E20" s="31"/>
+      <c r="F20" s="34">
         <v>2651.5</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>1632</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>50</v>
       </c>
       <c r="I20" s="1"/>
@@ -10781,23 +10789,23 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>46154</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="32">
         <v>485304</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="32">
         <v>404232</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <v>1516</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35">
+      <c r="F21" s="34"/>
+      <c r="G21" s="34">
         <v>3666</v>
       </c>
-      <c r="H21" s="35"/>
+      <c r="H21" s="34"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -10814,17 +10822,17 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>46155</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="48"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -10841,23 +10849,23 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <v>46156</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="32">
         <v>344042</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="32">
         <v>296318.25</v>
       </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="35">
+      <c r="E23" s="31"/>
+      <c r="F23" s="34">
         <v>310.75</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="34">
         <v>1656</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="34">
         <v>50</v>
       </c>
       <c r="I23" s="1"/>
@@ -10876,23 +10884,23 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="27">
         <v>46157</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="32">
         <v>509099</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <v>434826.5</v>
       </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="35">
+      <c r="E24" s="31"/>
+      <c r="F24" s="34">
         <v>140.5</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="34">
         <v>3192</v>
       </c>
-      <c r="H24" s="35"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="7"/>
@@ -10909,17 +10917,17 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="27">
         <v>46158</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="46"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -10936,17 +10944,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="18"/>
@@ -10963,23 +10971,23 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="27">
         <v>46160</v>
       </c>
       <c r="C27" s="12">
         <v>543461</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <v>461788.5</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="12">
         <v>14.5</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="33">
         <v>2784</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="30">
         <v>50</v>
       </c>
       <c r="I27" s="1"/>
@@ -10998,24 +11006,24 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="27">
         <v>46161</v>
       </c>
       <c r="C28" s="12">
         <v>524541</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="37">
         <v>448138.5</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="12">
         <v>386.5</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="33">
         <f>3660</f>
         <v>3660</v>
       </c>
-      <c r="H28" s="31"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -11032,23 +11040,23 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>46162</v>
       </c>
       <c r="C29" s="12">
         <v>276301</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="37">
         <v>237123.25</v>
       </c>
       <c r="E29" s="14">
         <v>334.25</v>
       </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="34">
+      <c r="G29" s="33">
         <v>1314</v>
       </c>
-      <c r="H29" s="31"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="7"/>
@@ -11065,24 +11073,24 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <v>46163</v>
       </c>
       <c r="C30" s="12">
         <v>412292</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="37">
         <v>343192.5</v>
       </c>
       <c r="E30" s="14">
         <v>1354.5</v>
       </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="34">
+      <c r="G30" s="33">
         <f>2166</f>
         <v>2166</v>
       </c>
-      <c r="H30" s="31">
+      <c r="H30" s="30">
         <v>50</v>
       </c>
       <c r="I30" s="1"/>
@@ -11101,17 +11109,17 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>46164</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="48"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="46"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="18"/>
@@ -11128,23 +11136,23 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>46165</v>
       </c>
       <c r="C32" s="12">
         <v>542169</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="37">
         <v>454961.25</v>
       </c>
       <c r="E32" s="14">
         <v>1166.25</v>
       </c>
       <c r="F32" s="12"/>
-      <c r="G32" s="34">
+      <c r="G32" s="33">
         <v>1602</v>
       </c>
-      <c r="H32" s="31"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -11161,17 +11169,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="46"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -11188,23 +11196,23 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>46167</v>
       </c>
-      <c r="C34" s="41">
+      <c r="C34" s="39">
         <v>429899</v>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="41">
         <v>386583</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12">
         <v>7262</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="33">
         <v>1740</v>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="30">
         <v>50</v>
       </c>
       <c r="I34" s="1"/>
@@ -11223,7 +11231,7 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <v>46168</v>
       </c>
       <c r="C35" s="12">
@@ -11236,10 +11244,10 @@
         <v>1630.25</v>
       </c>
       <c r="F35" s="12"/>
-      <c r="G35" s="34">
+      <c r="G35" s="33">
         <v>2352</v>
       </c>
-      <c r="H35" s="31"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -11256,23 +11264,23 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <v>46169</v>
       </c>
       <c r="C36" s="12">
         <v>253015</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="37">
         <v>217959</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12">
         <v>592</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="33">
         <v>630</v>
       </c>
-      <c r="H36" s="31"/>
+      <c r="H36" s="30"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -11289,7 +11297,7 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <v>46170</v>
       </c>
       <c r="C37" s="12">
@@ -11302,10 +11310,10 @@
         <v>2791</v>
       </c>
       <c r="F37" s="12"/>
-      <c r="G37" s="34">
+      <c r="G37" s="33">
         <v>948</v>
       </c>
-      <c r="H37" s="31"/>
+      <c r="H37" s="30"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -11322,15 +11330,25 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <v>46171</v>
       </c>
-      <c r="C38" s="25"/>
-      <c r="D38" s="39"/>
+      <c r="C38" s="12">
+        <v>364066</v>
+      </c>
+      <c r="D38" s="12">
+        <v>307115</v>
+      </c>
       <c r="E38" s="14"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="31"/>
+      <c r="F38" s="12">
+        <v>3571</v>
+      </c>
+      <c r="G38" s="33">
+        <v>2598</v>
+      </c>
+      <c r="H38" s="30">
+        <v>50</v>
+      </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7"/>
@@ -11347,17 +11365,17 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="27">
         <v>46172</v>
       </c>
-      <c r="C39" s="46" t="s">
+      <c r="C39" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -11374,17 +11392,17 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="46" t="s">
+      <c r="C40" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="48"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="46"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="7"/>
@@ -11401,12 +11419,12 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="28"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
       <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -11424,13 +11442,13 @@
       <c r="A42" s="22">
         <v>31</v>
       </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="48"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="46"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7"/>
@@ -11444,30 +11462,30 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19" ht="15">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="28"/>
+      <c r="B43" s="27"/>
       <c r="C43" s="17">
         <f>SUM(C10:C42)</f>
-        <v>8407252</v>
+        <v>8771318</v>
       </c>
       <c r="D43" s="17"/>
-      <c r="E43" s="29">
+      <c r="E43" s="28">
         <f>SUM(E10:E42)</f>
         <v>8867.5</v>
       </c>
       <c r="F43" s="17">
         <f>SUM(F10:F42)</f>
-        <v>14899.5</v>
+        <v>18470.5</v>
       </c>
       <c r="G43" s="17">
         <f>SUM(G10:G42)</f>
-        <v>42714</v>
+        <v>45312</v>
       </c>
       <c r="H43" s="17">
         <f>SUM(H10:H42)</f>
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -11486,7 +11504,7 @@
       <c r="B44" s="1"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="26"/>
+      <c r="E44" s="25"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="1"/>
@@ -14927,17 +14945,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/SHORT OVER ALL ROUTES - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B84630-1C33-4B26-8724-2CCD79D0E83E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A4D94A-93C8-466B-86E6-3E8AA0B04BEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MAY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -2003,7 +2003,10 @@
         <f>SUM(C10:C42)</f>
         <v>6841615.75</v>
       </c>
-      <c r="D43" s="17"/>
+      <c r="D43" s="17">
+        <f>SUM(D10,D13:D16,D20:D24,D28:D32,D34:D38)</f>
+        <v>5570570.7699999996</v>
+      </c>
       <c r="E43" s="28">
         <f>SUM(E10:E42)</f>
         <v>8295.5400000000009</v>
@@ -6731,7 +6734,10 @@
         <f>SUM(C10:C42)</f>
         <v>6279084</v>
       </c>
-      <c r="D43" s="17"/>
+      <c r="D43" s="17">
+        <f>SUM(D10,D13:D17,D20:D22,D24:D25,D27:D31,D32,D34:D38)</f>
+        <v>5329272.75</v>
+      </c>
       <c r="E43" s="28">
         <f>SUM(E10:E42)</f>
         <v>7998.5</v>
@@ -11470,7 +11476,10 @@
         <f>SUM(C10:C42)</f>
         <v>8771318</v>
       </c>
-      <c r="D43" s="17"/>
+      <c r="D43" s="17">
+        <f>SUM(D10:D11,D13:D17,D20:D21,D23:D24,D27:D30,D32,D34:D38)</f>
+        <v>7445311.5</v>
+      </c>
       <c r="E43" s="28">
         <f>SUM(E10:E42)</f>
         <v>8867.5</v>
@@ -14945,17 +14954,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
